--- a/content/xls/NSO_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_regions_01.01.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635EF57B-4977-451B-8734-CB2727E4D92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E3337-4048-4342-AD37-2198EDAEC316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="4615" yWindow="7766" windowWidth="23631" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -225,37 +225,34 @@
     <t>Численность населения, чел.</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уровень потребности в ДБО с учетом созданной альтернативной инфраструктуры </t>
-  </si>
-  <si>
     <t>Количество точек финансового доступа</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников 
-(учет ведется в разрезе населенных пунктов, в которых проживают Финансовые помощники)</t>
-  </si>
-  <si>
-    <t>Количество точек с банковским работником 
-(головной офис банка, его филиал или внутреннее структурное подразделение; мобильный банковский офис; удаленная точка с банковским работником)</t>
-  </si>
-  <si>
-    <t>Количество Отделений почтовой связи
-(стационарные отделения почтовой связи, передвижные отделения почтовой связи)</t>
-  </si>
-  <si>
-    <t>Количество банкоматов с функцией выдача наличных</t>
-  </si>
-  <si>
-    <t>Количество торгово-сервисных предприятий с сервисом "Выдача наличных на кассе"</t>
-  </si>
-  <si>
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры</t>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
+  </si>
+  <si>
+    <t>Количество Финансовых помощников</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
+  </si>
+  <si>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
   </si>
 </sst>
 </file>
@@ -266,7 +263,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,8 +280,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +298,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -322,10 +332,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -339,16 +350,26 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -660,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8ED133E-911A-4285-ABEA-63C58E8165A8}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="14.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -678,147 +699,147 @@
     <col min="13" max="13" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="98.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:13" ht="103.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>13847.999999999998</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>0.21153846153846168</v>
       </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0.21153846153846168</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.78846153846153832</v>
+      </c>
+      <c r="F2" s="10">
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
         <v>12</v>
       </c>
-      <c r="J2" s="2">
+      <c r="L2" s="2">
         <v>7</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0.78846153846153832</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
         <v>11175</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>0.24411764705882366</v>
       </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.24411764705882366</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.75588235294117634</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.30000000000000004</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
+        <v>4</v>
+      </c>
+      <c r="J3" s="9">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2">
         <v>21</v>
       </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>4</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0.75588235294117634</v>
+      <c r="L3" s="2">
+        <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>9042.0000000000036</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.1836000000000001</v>
       </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.1836000000000001</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.8163999999999999</v>
+      </c>
+      <c r="F4" s="10">
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -827,1127 +848,1133 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2">
         <v>17</v>
       </c>
-      <c r="J4" s="2">
+      <c r="L4" s="2">
         <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0.8163999999999999</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>14630</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>0.16653846153846164</v>
       </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.16653846153846164</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.83346153846153836</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.18000000000000005</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="9">
+        <v>4</v>
+      </c>
+      <c r="K5" s="2">
         <v>17</v>
       </c>
-      <c r="J5" s="2">
+      <c r="L5" s="2">
         <v>7</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0.83346153846153836</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>12573.999999999998</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.1306250000000001</v>
       </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.1306250000000001</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.8693749999999999</v>
+      </c>
+      <c r="F6" s="10">
         <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+      <c r="J6" s="9">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
         <v>6</v>
-      </c>
-      <c r="I6" s="2">
-        <v>15</v>
-      </c>
-      <c r="J6" s="2">
-        <v>6</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0.8693749999999999</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>11776.000000000002</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.12555555555555564</v>
       </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.12555555555555564</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.87444444444444436</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
         <v>16</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>5</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0.87444444444444436</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4">
         <v>57988.999999999993</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>0.21160714285714288</v>
       </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.21160714285714288</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.78839285714285712</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-0.45</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
+        <v>17</v>
+      </c>
+      <c r="J8" s="9">
+        <v>3</v>
+      </c>
+      <c r="K8" s="2">
         <v>22</v>
       </c>
-      <c r="J8" s="2">
+      <c r="L8" s="2">
         <v>33</v>
-      </c>
-      <c r="K8" s="2">
-        <v>17</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0.78839285714285712</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="4">
         <v>13325</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>0.18303030303030332</v>
       </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.18303030303030332</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.81696969696969668</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-0.05</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9">
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
         <v>17</v>
       </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.81696969696969668</v>
+      <c r="L9" s="2">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="4">
         <v>5291</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>0.16529411764705904</v>
       </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.16529411764705904</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.83470588235294096</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-0.1</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
         <v>1</v>
       </c>
-      <c r="I10" s="2">
+      <c r="K10" s="2">
         <v>11</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <v>1</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0.83470588235294096</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="4">
         <v>24203.000000000004</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>0.15375000000000005</v>
       </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.15375000000000005</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.84624999999999995</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-0.37</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="9">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2">
         <v>16</v>
       </c>
-      <c r="J11" s="2">
+      <c r="L11" s="2">
         <v>16</v>
-      </c>
-      <c r="K11" s="2">
-        <v>8</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0.84624999999999995</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
         <v>44353.999999999993</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>0.20540540540540553</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.18040540540540553</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
+      <c r="E12" s="5">
+        <v>0.79459459459459447</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-0.45</v>
       </c>
       <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
         <v>6</v>
       </c>
-      <c r="H12" s="2">
-        <v>15</v>
-      </c>
       <c r="I12" s="2">
+        <v>8</v>
+      </c>
+      <c r="J12" s="9">
+        <v>3</v>
+      </c>
+      <c r="K12" s="2">
         <v>19</v>
       </c>
-      <c r="J12" s="2">
+      <c r="L12" s="2">
         <v>25</v>
-      </c>
-      <c r="K12" s="2">
-        <v>8</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0.79459459459459447</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="4">
         <v>11524</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>0.11083333333333334</v>
       </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.11083333333333334</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.88916666666666666</v>
+      </c>
+      <c r="F13" s="10">
+        <v>-0.05</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
+        <v>2</v>
+      </c>
+      <c r="J13" s="9">
+        <v>4</v>
+      </c>
+      <c r="K13" s="2">
         <v>10</v>
       </c>
-      <c r="J13" s="2">
+      <c r="L13" s="2">
         <v>7</v>
-      </c>
-      <c r="K13" s="2">
-        <v>2</v>
-      </c>
-      <c r="L13" s="6">
-        <v>0.88916666666666666</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="4">
         <v>27615.000000000004</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>0.15709677419354862</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>2.6666666666666665E-2</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.13043010752688194</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
+      <c r="E14" s="5">
+        <v>0.84290322580645138</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-0.37</v>
       </c>
       <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
         <v>9</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
+        <v>22</v>
+      </c>
+      <c r="L14" s="2">
         <v>14</v>
-      </c>
-      <c r="I14" s="2">
-        <v>22</v>
-      </c>
-      <c r="J14" s="2">
-        <v>14</v>
-      </c>
-      <c r="K14" s="2">
-        <v>4</v>
-      </c>
-      <c r="L14" s="6">
-        <v>0.84290322580645138</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="4">
         <v>11205.000000000002</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>0.1940740740740744</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>3.6249999999999998E-2</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.15782407407407439</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15" s="5">
+        <v>0.8059259259259256</v>
+      </c>
+      <c r="F15" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="H15" s="2">
-        <v>4</v>
-      </c>
       <c r="I15" s="2">
+        <v>2</v>
+      </c>
+      <c r="J15" s="9">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
         <v>20</v>
       </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0.8059259259259256</v>
+      <c r="L15" s="2">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="4">
         <v>10013</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>0.163448275862069</v>
       </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.163448275862069</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.836551724137931</v>
+      </c>
+      <c r="F16" s="10">
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="9">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
         <v>22</v>
       </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0.836551724137931</v>
+      <c r="L16" s="2">
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="4">
         <v>8394.9999999999982</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>0.26000000000000012</v>
       </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.26000000000000012</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.73999999999999988</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.30000000000000004</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="9">
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
         <v>16</v>
       </c>
-      <c r="J17" s="2">
+      <c r="L17" s="2">
         <v>5</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0.73999999999999988</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="4">
         <v>23573</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>0.15600000000000014</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>0.02</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.13600000000000015</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
+      <c r="E18" s="5">
+        <v>0.84399999999999986</v>
+      </c>
+      <c r="F18" s="10">
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="G18" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2">
         <v>5</v>
       </c>
       <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" s="9">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
         <v>21</v>
       </c>
-      <c r="J18" s="2">
+      <c r="L18" s="2">
         <v>16</v>
-      </c>
-      <c r="K18" s="2">
-        <v>2</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0.84399999999999986</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="4">
         <v>40472</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>0.17878787878787905</v>
       </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.17878787878787905</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.82121212121212095</v>
+      </c>
+      <c r="F19" s="10">
+        <v>0.18000000000000005</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
+        <v>13</v>
+      </c>
+      <c r="J19" s="9">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2">
         <v>27</v>
       </c>
-      <c r="J19" s="2">
+      <c r="L19" s="2">
         <v>20</v>
-      </c>
-      <c r="K19" s="2">
-        <v>13</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0.82121212121212095</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>181340</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>0.15206349206349179</v>
       </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.15206349206349179</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.84793650793650821</v>
+      </c>
+      <c r="F20" s="10">
         <v>0</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
+        <v>72</v>
+      </c>
+      <c r="J20" s="9">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2">
         <v>34</v>
       </c>
-      <c r="J20" s="2">
+      <c r="L20" s="2">
         <v>106</v>
-      </c>
-      <c r="K20" s="2">
-        <v>72</v>
-      </c>
-      <c r="L20" s="6">
-        <v>0.84793650793650821</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="4">
         <v>33533</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>0.12176470588235322</v>
       </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.12176470588235322</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.87823529411764678</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0.30000000000000004</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>11</v>
+      </c>
+      <c r="J21" s="9">
+        <v>4</v>
+      </c>
+      <c r="K21" s="2">
         <v>23</v>
       </c>
-      <c r="I21" s="2">
-        <v>23</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="L21" s="2">
         <v>12</v>
-      </c>
-      <c r="K21" s="2">
-        <v>11</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0.87823529411764678</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="4">
         <v>7258</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>0.17307692307692324</v>
       </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.17307692307692324</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.82692307692307676</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-0.45</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="9">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
+        <v>10</v>
+      </c>
+      <c r="L22" s="2">
         <v>2</v>
-      </c>
-      <c r="I22" s="2">
-        <v>10</v>
-      </c>
-      <c r="J22" s="2">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0.82692307692307676</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="4">
         <v>31325.000000000004</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>0.16964285714285732</v>
       </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.16964285714285732</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.83035714285714268</v>
+      </c>
+      <c r="F23" s="10">
+        <v>-0.05</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
+        <v>3</v>
+      </c>
+      <c r="J23" s="9">
+        <v>2</v>
+      </c>
+      <c r="K23" s="2">
         <v>17</v>
       </c>
-      <c r="J23" s="2">
+      <c r="L23" s="2">
         <v>19</v>
-      </c>
-      <c r="K23" s="2">
-        <v>3</v>
-      </c>
-      <c r="L23" s="6">
-        <v>0.83035714285714268</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4">
         <v>12495.999999999996</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>0.31771428571428584</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="E24" s="6">
-        <v>0.28021428571428586</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="E24" s="5">
+        <v>0.68228571428571416</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G24" s="2">
         <v>1</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <v>10</v>
       </c>
-      <c r="H24" s="2">
-        <v>6</v>
-      </c>
       <c r="I24" s="2">
+        <v>12</v>
+      </c>
+      <c r="J24" s="9">
+        <v>3</v>
+      </c>
+      <c r="K24" s="2">
         <v>8</v>
       </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2">
-        <v>12</v>
-      </c>
-      <c r="L24" s="6">
-        <v>0.68228571428571416</v>
+      <c r="L24" s="2">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="4">
         <v>32597</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>0.22559322033898288</v>
       </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.22559322033898288</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.77440677966101712</v>
+      </c>
+      <c r="F25" s="10">
+        <v>-0.37</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
+        <v>5</v>
+      </c>
+      <c r="J25" s="9">
+        <v>4</v>
+      </c>
+      <c r="K25" s="2">
         <v>28</v>
       </c>
-      <c r="J25" s="2">
+      <c r="L25" s="2">
         <v>6</v>
-      </c>
-      <c r="K25" s="2">
-        <v>5</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0.77440677966101712</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="4">
         <v>10716</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>0.15000000000000002</v>
       </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="F26" s="10">
+        <v>-0.45</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26" s="9">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2">
         <v>15</v>
       </c>
-      <c r="J26" s="2">
+      <c r="L26" s="2">
         <v>5</v>
-      </c>
-      <c r="K26" s="2">
-        <v>9</v>
-      </c>
-      <c r="L26" s="6">
-        <v>0.85</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="4">
         <v>10216</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>0.24333333333333351</v>
       </c>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.24333333333333351</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.75666666666666649</v>
+      </c>
+      <c r="F27" s="10">
+        <v>-0.05</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2">
+        <v>13</v>
+      </c>
+      <c r="L27" s="2">
         <v>5</v>
-      </c>
-      <c r="I27" s="2">
-        <v>13</v>
-      </c>
-      <c r="J27" s="2">
-        <v>5</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
-        <v>0.75666666666666649</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="4">
         <v>20330.000000000004</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>0.18487804878048797</v>
       </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.18487804878048797</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
+      <c r="D28" s="5">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.81512195121951203</v>
+      </c>
+      <c r="F28" s="10">
+        <v>-0.37</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
+        <v>3</v>
+      </c>
+      <c r="J28" s="9">
+        <v>3</v>
+      </c>
+      <c r="K28" s="2">
         <v>23</v>
       </c>
-      <c r="J28" s="2">
+      <c r="L28" s="2">
         <v>13</v>
-      </c>
-      <c r="K28" s="2">
-        <v>3</v>
-      </c>
-      <c r="L28" s="6">
-        <v>0.81512195121951203</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="4">
         <v>29097</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>0.21538461538461562</v>
       </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.21538461538461562</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.78461538461538438</v>
+      </c>
+      <c r="F29" s="10">
+        <v>-0.1</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9">
+        <v>4</v>
+      </c>
+      <c r="K29" s="2">
         <v>19</v>
       </c>
-      <c r="J29" s="2">
+      <c r="L29" s="2">
         <v>6</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6">
-        <v>0.78461538461538438</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="4">
         <v>13816</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>0.20400000000000007</v>
       </c>
-      <c r="D30" s="6">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.20400000000000007</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.79599999999999993</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0.7</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2">
+        <v>15</v>
+      </c>
+      <c r="L30" s="2">
         <v>6</v>
-      </c>
-      <c r="I30" s="2">
-        <v>15</v>
-      </c>
-      <c r="J30" s="2">
-        <v>6</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="6">
-        <v>0.79599999999999993</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="4">
         <v>7668</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>0.22705882352941198</v>
       </c>
-      <c r="D31" s="6">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.22705882352941198</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.77294117647058802</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0.9</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="9">
         <v>2</v>
       </c>
-      <c r="I31" s="2">
+      <c r="K31" s="2">
         <v>14</v>
       </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6">
-        <v>0.77294117647058802</v>
+      <c r="L31" s="2">
+        <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>61</v>
       </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J33" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/content/xls/NSO_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_regions_01.01.2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E3337-4048-4342-AD37-2198EDAEC316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031ED2C9-BA05-4880-A7A3-A120BAF79D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4615" yWindow="7766" windowWidth="23631" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -231,12 +231,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
-  </si>
-  <si>
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
@@ -253,6 +247,12 @@
   </si>
   <si>
     <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -707,34 +707,34 @@
         <v>62</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>

--- a/content/xls/NSO_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_regions_01.01.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031ED2C9-BA05-4880-A7A3-A120BAF79D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9585F006-34D2-4D03-AABB-4D8615EB7B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="2942" yWindow="5391" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -252,16 +252,17 @@
     <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_-\ #,##0.00_-;\-\ #,##0.00_-;_-\ &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -360,11 +361,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -687,7 +688,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -699,7 +700,7 @@
     <col min="13" max="13" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="103.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="118.15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -745,19 +746,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>13847.999999999998</v>
+        <v>13848</v>
       </c>
       <c r="C2" s="5">
-        <v>0.21153846153846168</v>
-      </c>
-      <c r="D2" s="5">
+        <v>0.32899999999999996</v>
+      </c>
+      <c r="D2" s="9">
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>0.78846153846153832</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="F2" s="10">
-        <v>9.9999999999999978E-2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -768,14 +769,14 @@
       <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="9">
-        <v>1</v>
+      <c r="J2" s="2">
+        <v>3</v>
       </c>
       <c r="K2" s="2">
         <v>12</v>
       </c>
       <c r="L2" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>32</v>
@@ -789,16 +790,16 @@
         <v>11175</v>
       </c>
       <c r="C3" s="5">
-        <v>0.24411764705882366</v>
-      </c>
-      <c r="D3" s="5">
+        <v>0.33699999999999997</v>
+      </c>
+      <c r="D3" s="9">
         <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>0.75588235294117634</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="F3" s="10">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -807,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>4</v>
-      </c>
-      <c r="J3" s="9">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
       </c>
       <c r="K3" s="2">
         <v>21</v>
@@ -827,19 +828,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>9042.0000000000036</v>
+        <v>9042</v>
       </c>
       <c r="C4" s="5">
-        <v>0.1836000000000001</v>
-      </c>
-      <c r="D4" s="5">
+        <v>0.18600000000000005</v>
+      </c>
+      <c r="D4" s="9">
         <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>0.8163999999999999</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="F4" s="10">
-        <v>5.0000000000000044E-2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -850,11 +851,11 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="9">
-        <v>3</v>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2">
         <v>1</v>
@@ -871,16 +872,16 @@
         <v>14630</v>
       </c>
       <c r="C5" s="5">
-        <v>0.16653846153846164</v>
-      </c>
-      <c r="D5" s="5">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="D5" s="9">
         <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>0.83346153846153836</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="F5" s="10">
-        <v>0.18000000000000005</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -889,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>6</v>
       </c>
       <c r="K5" s="2">
         <v>17</v>
       </c>
       <c r="L5" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>35</v>
@@ -909,16 +910,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>12573.999999999998</v>
+        <v>12574</v>
       </c>
       <c r="C6" s="5">
-        <v>0.1306250000000001</v>
-      </c>
-      <c r="D6" s="5">
+        <v>0.128</v>
+      </c>
+      <c r="D6" s="9">
         <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>0.8693749999999999</v>
+        <v>0.872</v>
       </c>
       <c r="F6" s="10">
         <v>0</v>
@@ -932,14 +933,14 @@
       <c r="I6" s="2">
         <v>3</v>
       </c>
-      <c r="J6" s="9">
-        <v>1</v>
+      <c r="J6" s="2">
+        <v>6</v>
       </c>
       <c r="K6" s="2">
         <v>15</v>
       </c>
       <c r="L6" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
@@ -950,19 +951,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>11776.000000000002</v>
+        <v>11776</v>
       </c>
       <c r="C7" s="5">
-        <v>0.12555555555555564</v>
-      </c>
-      <c r="D7" s="5">
+        <v>0.16600000000000004</v>
+      </c>
+      <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>0.87444444444444436</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="F7" s="10">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -973,14 +974,14 @@
       <c r="I7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="9">
-        <v>2</v>
+      <c r="J7" s="2">
+        <v>6</v>
       </c>
       <c r="K7" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>37</v>
@@ -991,19 +992,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>57988.999999999993</v>
+        <v>57989</v>
       </c>
       <c r="C8" s="5">
-        <v>0.21160714285714288</v>
-      </c>
-      <c r="D8" s="5">
+        <v>0.20899999999999996</v>
+      </c>
+      <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>0.78839285714285712</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="F8" s="10">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -1014,14 +1015,14 @@
       <c r="I8" s="2">
         <v>17</v>
       </c>
-      <c r="J8" s="9">
-        <v>3</v>
+      <c r="J8" s="2">
+        <v>12</v>
       </c>
       <c r="K8" s="2">
         <v>22</v>
       </c>
       <c r="L8" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
@@ -1035,16 +1036,16 @@
         <v>13325</v>
       </c>
       <c r="C9" s="5">
-        <v>0.18303030303030332</v>
-      </c>
-      <c r="D9" s="5">
+        <v>0.19199999999999995</v>
+      </c>
+      <c r="D9" s="9">
         <v>0</v>
       </c>
       <c r="E9" s="5">
-        <v>0.81696969696969668</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F9" s="10">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1055,11 +1056,11 @@
       <c r="I9" s="2">
         <v>1</v>
       </c>
-      <c r="J9" s="9">
-        <v>4</v>
+      <c r="J9" s="2">
+        <v>6</v>
       </c>
       <c r="K9" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1076,16 +1077,16 @@
         <v>5291</v>
       </c>
       <c r="C10" s="5">
-        <v>0.16529411764705904</v>
-      </c>
-      <c r="D10" s="5">
+        <v>0.255</v>
+      </c>
+      <c r="D10" s="9">
         <v>0</v>
       </c>
       <c r="E10" s="5">
-        <v>0.83470588235294096</v>
+        <v>0.745</v>
       </c>
       <c r="F10" s="10">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -1096,7 +1097,7 @@
       <c r="I10" s="2">
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="2">
         <v>1</v>
       </c>
       <c r="K10" s="2">
@@ -1114,19 +1115,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>24203.000000000004</v>
+        <v>24203</v>
       </c>
       <c r="C11" s="5">
-        <v>0.15375000000000005</v>
-      </c>
-      <c r="D11" s="5">
+        <v>0.16400000000000003</v>
+      </c>
+      <c r="D11" s="9">
         <v>0</v>
       </c>
       <c r="E11" s="5">
-        <v>0.84624999999999995</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="F11" s="10">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -1137,14 +1138,14 @@
       <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="J11" s="9">
-        <v>2</v>
+      <c r="J11" s="2">
+        <v>9</v>
       </c>
       <c r="K11" s="2">
         <v>16</v>
       </c>
       <c r="L11" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>41</v>
@@ -1155,37 +1156,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>44353.999999999993</v>
+        <v>44354</v>
       </c>
       <c r="C12" s="5">
-        <v>0.20540540540540553</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
       </c>
       <c r="E12" s="5">
-        <v>0.79459459459459447</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="10">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
-      </c>
-      <c r="J12" s="9">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="J12" s="2">
+        <v>14</v>
       </c>
       <c r="K12" s="2">
         <v>19</v>
       </c>
       <c r="L12" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>42</v>
@@ -1199,16 +1200,16 @@
         <v>11524</v>
       </c>
       <c r="C13" s="5">
-        <v>0.11083333333333334</v>
-      </c>
-      <c r="D13" s="5">
+        <v>0.16900000000000004</v>
+      </c>
+      <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="5">
-        <v>0.88916666666666666</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="F13" s="10">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
@@ -1219,14 +1220,14 @@
       <c r="I13" s="2">
         <v>2</v>
       </c>
-      <c r="J13" s="9">
-        <v>4</v>
+      <c r="J13" s="2">
+        <v>7</v>
       </c>
       <c r="K13" s="2">
         <v>10</v>
       </c>
       <c r="L13" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>43</v>
@@ -1237,37 +1238,37 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>27615.000000000004</v>
+        <v>27615</v>
       </c>
       <c r="C14" s="5">
-        <v>0.15709677419354862</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.6666666666666665E-2</v>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
       </c>
       <c r="E14" s="5">
-        <v>0.84290322580645138</v>
+        <v>0.84</v>
       </c>
       <c r="F14" s="10">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>4</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>15</v>
       </c>
       <c r="K14" s="2">
         <v>22</v>
       </c>
       <c r="L14" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>44</v>
@@ -1278,31 +1279,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>11205.000000000002</v>
+        <v>11205</v>
       </c>
       <c r="C15" s="5">
-        <v>0.1940740740740744</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3.6249999999999998E-2</v>
+        <v>0.19699999999999995</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
       </c>
       <c r="E15" s="5">
-        <v>0.8059259259259256</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="F15" s="10">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
         <v>1</v>
       </c>
-      <c r="H15" s="2">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2">
-        <v>2</v>
-      </c>
-      <c r="J15" s="9">
-        <v>2</v>
+      <c r="J15" s="2">
+        <v>4</v>
       </c>
       <c r="K15" s="2">
         <v>20</v>
@@ -1322,16 +1323,16 @@
         <v>10013</v>
       </c>
       <c r="C16" s="5">
-        <v>0.163448275862069</v>
-      </c>
-      <c r="D16" s="5">
+        <v>0.16600000000000004</v>
+      </c>
+      <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="5">
-        <v>0.836551724137931</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="F16" s="10">
-        <v>9.9999999999999978E-2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -1342,8 +1343,8 @@
       <c r="I16" s="2">
         <v>1</v>
       </c>
-      <c r="J16" s="9">
-        <v>3</v>
+      <c r="J16" s="2">
+        <v>2</v>
       </c>
       <c r="K16" s="2">
         <v>22</v>
@@ -1360,19 +1361,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>8394.9999999999982</v>
+        <v>8395</v>
       </c>
       <c r="C17" s="5">
-        <v>0.26000000000000012</v>
-      </c>
-      <c r="D17" s="5">
+        <v>0.32799999999999996</v>
+      </c>
+      <c r="D17" s="9">
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>0.73999999999999988</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="F17" s="10">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -1383,14 +1384,14 @@
       <c r="I17" s="2">
         <v>1</v>
       </c>
-      <c r="J17" s="9">
-        <v>4</v>
+      <c r="J17" s="2">
+        <v>3</v>
       </c>
       <c r="K17" s="2">
         <v>16</v>
       </c>
       <c r="L17" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>47</v>
@@ -1404,34 +1405,34 @@
         <v>23573</v>
       </c>
       <c r="C18" s="5">
-        <v>0.15600000000000014</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.02</v>
+        <v>0.15500000000000003</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
       </c>
       <c r="E18" s="5">
-        <v>0.84399999999999986</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="F18" s="10">
-        <v>5.0000000000000044E-2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>2</v>
       </c>
-      <c r="J18" s="9">
-        <v>1</v>
+      <c r="J18" s="2">
+        <v>5</v>
       </c>
       <c r="K18" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L18" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>48</v>
@@ -1445,16 +1446,16 @@
         <v>40472</v>
       </c>
       <c r="C19" s="5">
-        <v>0.17878787878787905</v>
-      </c>
-      <c r="D19" s="5">
+        <v>0.17700000000000005</v>
+      </c>
+      <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="5">
-        <v>0.82121212121212095</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="F19" s="10">
-        <v>0.18000000000000005</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1463,16 +1464,16 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>13</v>
-      </c>
-      <c r="J19" s="9">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="J19" s="2">
+        <v>7</v>
       </c>
       <c r="K19" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L19" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>49</v>
@@ -1483,16 +1484,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>181340</v>
+        <v>160478</v>
       </c>
       <c r="C20" s="5">
-        <v>0.15206349206349179</v>
-      </c>
-      <c r="D20" s="5">
+        <v>0.15200000000000002</v>
+      </c>
+      <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="5">
-        <v>0.84793650793650821</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="F20" s="10">
         <v>0</v>
@@ -1504,16 +1505,16 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>72</v>
-      </c>
-      <c r="J20" s="9">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="J20" s="2">
+        <v>15</v>
       </c>
       <c r="K20" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L20" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>50</v>
@@ -1527,16 +1528,16 @@
         <v>33533</v>
       </c>
       <c r="C21" s="5">
-        <v>0.12176470588235322</v>
-      </c>
-      <c r="D21" s="5">
+        <v>0.122</v>
+      </c>
+      <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="5">
-        <v>0.87823529411764678</v>
+        <v>0.878</v>
       </c>
       <c r="F21" s="10">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -1545,16 +1546,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>11</v>
-      </c>
-      <c r="J21" s="9">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="J21" s="2">
+        <v>26</v>
       </c>
       <c r="K21" s="2">
         <v>23</v>
       </c>
       <c r="L21" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>51</v>
@@ -1568,16 +1569,16 @@
         <v>7258</v>
       </c>
       <c r="C22" s="5">
-        <v>0.17307692307692324</v>
-      </c>
-      <c r="D22" s="5">
+        <v>0.17800000000000005</v>
+      </c>
+      <c r="D22" s="9">
         <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>0.82692307692307676</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="F22" s="10">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -1588,11 +1589,11 @@
       <c r="I22" s="2">
         <v>1</v>
       </c>
-      <c r="J22" s="9">
-        <v>1</v>
+      <c r="J22" s="2">
+        <v>2</v>
       </c>
       <c r="K22" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L22" s="2">
         <v>2</v>
@@ -1606,19 +1607,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>31325.000000000004</v>
+        <v>31325</v>
       </c>
       <c r="C23" s="5">
-        <v>0.16964285714285732</v>
-      </c>
-      <c r="D23" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D23" s="9">
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>0.83035714285714268</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="F23" s="10">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -1629,14 +1630,14 @@
       <c r="I23" s="2">
         <v>3</v>
       </c>
-      <c r="J23" s="9">
-        <v>2</v>
+      <c r="J23" s="2">
+        <v>12</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
       </c>
       <c r="L23" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>53</v>
@@ -1647,31 +1648,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>12495.999999999996</v>
+        <v>12496</v>
       </c>
       <c r="C24" s="5">
-        <v>0.31771428571428584</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3.7499999999999999E-2</v>
+        <v>0.45899999999999996</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>0.68228571428571416</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="F24" s="10">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>12</v>
-      </c>
-      <c r="J24" s="9">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>6</v>
       </c>
       <c r="K24" s="2">
         <v>8</v>
@@ -1691,16 +1692,16 @@
         <v>32597</v>
       </c>
       <c r="C25" s="5">
-        <v>0.22559322033898288</v>
-      </c>
-      <c r="D25" s="5">
+        <v>0.22299999999999998</v>
+      </c>
+      <c r="D25" s="9">
         <v>0</v>
       </c>
       <c r="E25" s="5">
-        <v>0.77440677966101712</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="F25" s="10">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -1709,16 +1710,16 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>5</v>
-      </c>
-      <c r="J25" s="9">
         <v>4</v>
+      </c>
+      <c r="J25" s="2">
+        <v>12</v>
       </c>
       <c r="K25" s="2">
         <v>28</v>
       </c>
       <c r="L25" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>55</v>
@@ -1732,16 +1733,16 @@
         <v>10716</v>
       </c>
       <c r="C26" s="5">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="D26" s="5">
+        <v>0.19299999999999995</v>
+      </c>
+      <c r="D26" s="9">
         <v>0</v>
       </c>
       <c r="E26" s="5">
-        <v>0.85</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="F26" s="10">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -1752,14 +1753,14 @@
       <c r="I26" s="2">
         <v>9</v>
       </c>
-      <c r="J26" s="9">
-        <v>1</v>
+      <c r="J26" s="2">
+        <v>4</v>
       </c>
       <c r="K26" s="2">
         <v>15</v>
       </c>
       <c r="L26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>56</v>
@@ -1773,16 +1774,16 @@
         <v>10216</v>
       </c>
       <c r="C27" s="5">
-        <v>0.24333333333333351</v>
-      </c>
-      <c r="D27" s="5">
+        <v>0.23299999999999998</v>
+      </c>
+      <c r="D27" s="9">
         <v>0</v>
       </c>
       <c r="E27" s="5">
-        <v>0.75666666666666649</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="F27" s="10">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
@@ -1793,14 +1794,14 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="9">
-        <v>2</v>
+      <c r="J27" s="2">
+        <v>5</v>
       </c>
       <c r="K27" s="2">
         <v>13</v>
       </c>
       <c r="L27" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>57</v>
@@ -1811,19 +1812,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>20330.000000000004</v>
+        <v>20330</v>
       </c>
       <c r="C28" s="5">
-        <v>0.18487804878048797</v>
-      </c>
-      <c r="D28" s="5">
+        <v>0.29200000000000004</v>
+      </c>
+      <c r="D28" s="9">
         <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>0.81512195121951203</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="F28" s="10">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -1832,16 +1833,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>3</v>
-      </c>
-      <c r="J28" s="9">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="J28" s="2">
+        <v>10</v>
       </c>
       <c r="K28" s="2">
         <v>23</v>
       </c>
       <c r="L28" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>58</v>
@@ -1855,16 +1856,16 @@
         <v>29097</v>
       </c>
       <c r="C29" s="5">
-        <v>0.21538461538461562</v>
-      </c>
-      <c r="D29" s="5">
+        <v>0.21399999999999997</v>
+      </c>
+      <c r="D29" s="9">
         <v>0</v>
       </c>
       <c r="E29" s="5">
-        <v>0.78461538461538438</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="F29" s="10">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -1873,16 +1874,16 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="9">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="J29" s="2">
+        <v>6</v>
       </c>
       <c r="K29" s="2">
         <v>19</v>
       </c>
       <c r="L29" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>59</v>
@@ -1896,16 +1897,16 @@
         <v>13816</v>
       </c>
       <c r="C30" s="5">
-        <v>0.20400000000000007</v>
-      </c>
-      <c r="D30" s="5">
+        <v>0.29900000000000004</v>
+      </c>
+      <c r="D30" s="9">
         <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>0.79599999999999993</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="F30" s="10">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -1916,14 +1917,14 @@
       <c r="I30" s="2">
         <v>1</v>
       </c>
-      <c r="J30" s="9">
-        <v>1</v>
+      <c r="J30" s="2">
+        <v>6</v>
       </c>
       <c r="K30" s="2">
         <v>15</v>
       </c>
       <c r="L30" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>60</v>
@@ -1937,16 +1938,16 @@
         <v>7668</v>
       </c>
       <c r="C31" s="5">
-        <v>0.22705882352941198</v>
-      </c>
-      <c r="D31" s="5">
+        <v>0.16800000000000004</v>
+      </c>
+      <c r="D31" s="9">
         <v>0</v>
       </c>
       <c r="E31" s="5">
-        <v>0.77294117647058802</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="F31" s="10">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
@@ -1957,11 +1958,11 @@
       <c r="I31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="2">
         <v>2</v>
       </c>
       <c r="K31" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L31" s="2">
         <v>0</v>

--- a/content/xls/NSO_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_regions_01.01.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9585F006-34D2-4D03-AABB-4D8615EB7B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2415332-44C1-4BFC-AD78-67717088A6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2942" yWindow="5391" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -234,9 +234,6 @@
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников</t>
-  </si>
-  <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
   </si>
 </sst>
 </file>
@@ -708,10 +708,10 @@
         <v>62</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>64</v>
@@ -723,19 +723,19 @@
         <v>63</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>31</v>
